--- a/data/seed/portfolio/L-2024-3304/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-3304/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>93813000</v>
+        <v>9856000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Andijon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>292567706</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000923047387001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №166/26 от 01.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6988</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>35419000</v>
+        <v>21230000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Navro'z Polimer XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>297333616</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000293550767001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5163</t>
+          <t>Mahsulot uchun to'lov, shartn. №126/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>24760000</v>
+        <v>14983000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №141/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №9605 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>117531000</v>
+        <v>12331000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9851 ОТ 03.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №364 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -722,33 +722,28 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>239742000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>134223000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>244420232</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7384 за поставленный товар</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №3471</t>
         </is>
       </c>
     </row>
@@ -763,40 +758,40 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>33991000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>187786000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6978</t>
+          <t>Оплата за сырье по договору №6/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -806,38 +801,38 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>14627000</v>
+        <v>65063000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №134/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6561 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -845,23 +840,23 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>32082000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>22233000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -871,14 +866,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №224/26</t>
+          <t>Оплата за продукцию по дог. №215/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -886,23 +881,23 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>56433000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>11603000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -912,14 +907,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №7610</t>
+          <t>Mahsulot uchun to'lov, shartn. №195/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -928,34 +923,39 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>134223000</v>
+        <v>17851000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>339870886</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000153283399001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА ИЮНЬ 2026 Г. СОГЛАСНО РЕЕСТРУ №1287</t>
+          <t>Арендная плата за июль 2026 г. по договору №65/23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -963,23 +963,23 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>136575000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>36886000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -989,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6516</t>
+          <t>Оплата по счет-фактуре №7395 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,40 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>40878000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>409411000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1288 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №181/26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1046,39 +1046,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>72104000</v>
+        <v>69809000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1276</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №222/26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>23197000</v>
+        <v>134529000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №113/26 от 09.07.2026</t>
+          <t>Shartnoma №282/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>17851000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>20627000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>395726929</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000499848805001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №31/24</t>
+          <t>Предоплата за товар по договору №204/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>132896000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>10756000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №8735</t>
+          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>26060000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>57425000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №496 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartn. №53/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,33 +1250,33 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>24060000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>69054000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №58/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №272/26</t>
         </is>
       </c>
     </row>
@@ -1291,23 +1291,23 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>55014000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>788769000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1317,14 +1317,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №14/26 от 13.07.2026</t>
+          <t>Предоплата за материалы по дог. №63/26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>22837000</v>
+        <v>13389000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6512 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №4/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>18985000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>18303000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
+          <t>Ijtimoiy soliq yun 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1415,32 +1415,32 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>168537000</v>
+        <v>18303000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5886</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
     </row>
@@ -1455,33 +1455,33 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>35125000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>198501000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shartnoma №277/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №140/26</t>
         </is>
       </c>
     </row>
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>18303000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>96716000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №241/26 от 15.07.2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,33 +1537,33 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>18303000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>14052000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JSHDS IYUN OYI UCHUN</t>
+          <t>Оплата по с/ф №2149 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1580,31 +1580,31 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>30953000</v>
+        <v>14199000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Navro'z Non MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>267055674</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000453631094001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2436 за поставленный товар</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №185/26 ОТ 17.07.2026</t>
         </is>
       </c>
     </row>
@@ -1621,38 +1621,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>13556000</v>
+        <v>10483000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6805 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №62/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1662,38 +1662,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>13432000</v>
+        <v>40215000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №41/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7602 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1703,38 +1703,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>195734000</v>
+        <v>47330000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Shartnoma №206/26 bo'yicha oldindan to'lov</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №201/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1744,21 +1744,21 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>132904000</v>
+        <v>14864000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1768,14 +1768,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9425 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №38/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>10612000</v>
+        <v>12148000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №33/26, НДС 12%</t>
+          <t>Оплата по с/ф №5178 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1824,23 +1824,23 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>53452000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>137730000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №240/26</t>
+          <t>Оплата по счет-фактуре №7774 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1865,40 +1865,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>53876000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>26117000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Namangan Moy MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>335189064</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000150998941001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3402</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №146/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1906,40 +1906,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>572792000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>25363000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Andijon Meva-Sabzavot AJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>323554683</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000641184978001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5943</t>
+          <t>Оплата за товар по счет-фактуре №7058 от 22.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1947,40 +1947,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>16945000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>28673000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №207/26, НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1990,38 +1990,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>10348000</v>
+        <v>765833000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №28/26 от 21.07.2026</t>
+          <t>Оплата за продукцию по дог. №249/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2029,40 +2029,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>29269000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>64492000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Non XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305567444</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000363109450001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮНЬ</t>
+          <t>Оплата за товар по счет-фактуре №5358 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2072,38 +2072,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>507458000</v>
+        <v>14176000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №144/26 от 22.07.2026</t>
+          <t>Оплата по счет-фактуре №5390 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2113,38 +2113,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>57258000</v>
+        <v>113074000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>212402443</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000886958340001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9705 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3463 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2154,38 +2154,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>47462000</v>
+        <v>44697000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №65/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №9343 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2193,23 +2193,23 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>436644000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>15688000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №182</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №757</t>
         </is>
       </c>
     </row>
@@ -2236,38 +2236,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>18027000</v>
+        <v>13960000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5721 за поставленный товар</t>
+          <t>Предоплата за товар по договору №221/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>25.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2275,40 +2275,35 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>16361000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>230500000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>244420232</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>16307000256038610417</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2316,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>57175000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>65079000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5078</t>
+          <t>Оплата за товар по с/ф №9561 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2357,28 +2352,33 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>230500000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>60161000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>16307000256038610417</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №77/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2395,31 +2395,31 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>30783000</v>
+        <v>25611000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №6169 ОТ 27.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №31/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
@@ -2436,31 +2436,31 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>24627000</v>
+        <v>11022000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9155 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №67 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2475,33 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>23075000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>11157000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000627281556001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №199/26 от 27.07.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
@@ -2516,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>13862000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>76294000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6360 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1672</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,23 +2557,23 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>11157000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>36282000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000683921538001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2583,14 +2583,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Предоплата за товар по договору №47/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,33 +2598,33 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>207999000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>35740000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tovalar uchun to'lov h/f №4904</t>
+          <t>Предоплата за товар по договору №178/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
@@ -2639,40 +2639,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>146553000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>168807000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №173/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №103/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>118171000</v>
+        <v>110475000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №232/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3290 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2723,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>32525000</v>
+        <v>73975000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6691 ОТ 28.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №182/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,23 +2762,23 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>74958000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>96098000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №146/26</t>
+          <t>Оплата по счет-фактуре №9671 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,38 +2805,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>46160000</v>
+        <v>17357000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №121/26 ОТ 30.07.2026</t>
+          <t>Оплата за продукцию по договору №116/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2846,38 +2846,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>33911000</v>
+        <v>12982000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №72/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7969</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,40 +2885,35 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>24223000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>205381056</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №242/26 от 30.07.2026</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2928,38 +2923,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>17636000</v>
+        <v>1254775000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №3552 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2969,38 +2964,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>8413000</v>
+        <v>19345000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Gulshan Non XK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>305567444</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000363109450001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №17/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №6494 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3008,40 +3003,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>42047000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>51258000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1690 31.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3050,34 +3045,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>300000</v>
+        <v>99628000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Samarqand Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за товары согласно счет-фактуре №4491</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3086,32 +3086,27 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>23094000</v>
+        <v>133664000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Andijon Meva-Sabzavot AJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>323554683</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000641184978001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №134/26</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №7976</t>
         </is>
       </c>
     </row>
@@ -3128,38 +3123,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>25481000</v>
+        <v>31408000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2001 за поставленный товар</t>
+          <t>Предоплата за товар по договору №178/26 от 05.08.2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3167,23 +3162,23 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>43094000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>11740000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3193,14 +3188,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8321</t>
+          <t>Предоплата за товар по дог. №201/26 от 05.08.2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,39 +3204,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>50956000</v>
+        <v>82420000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №130/26 от 06.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №201/26 от 07.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3249,28 +3244,33 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>133664000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>162109000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ЗАРАБОТНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
+          <t>Оплата за товар по счет-фактуре №5240 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3287,21 +3287,21 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>41369000</v>
+        <v>24718000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Urganch Avto Savdo MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>326351890</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000431509989001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2188 за поставленный товар</t>
+          <t>Shartnoma №26/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -3328,31 +3328,31 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>28268000</v>
+        <v>22802000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>212402443</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000886958340001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5246 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №246/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3367,23 +3367,23 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>14205000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>17777000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>339870886</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000153283399001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9398 10.08.2026, QQS bilan</t>
+          <t>Арендная плата за август 2026 г. по договору №65/23</t>
         </is>
       </c>
     </row>
@@ -3409,39 +3409,39 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>17777000</v>
+        <v>46990000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>395726929</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000499848805001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №31/24</t>
+          <t>Оплата за упаковочные материалы, с/ф №1418</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3449,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>24416000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>137367000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Namangan Moy MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>335189064</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000150998941001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №181/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9077</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,23 +3490,23 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>157038000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>13743000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №133/26 от 10.08.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №247/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
@@ -3533,38 +3533,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>138253000</v>
+        <v>10348000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>212402443</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000886958340001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shartnoma №245/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №86/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3572,40 +3572,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>71493000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>490848000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bekobod Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>255468386</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000118497862001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №10 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №7153</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3615,38 +3615,38 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>36307000</v>
+        <v>19691000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №76/26 от 11.08.2026</t>
+          <t>Оплата за родукцию по договору №15/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,23 +3654,23 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>1216818000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>54279000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №258/26</t>
+          <t>Оплата по счет-фактуре №8913 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3697,31 +3697,31 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>66356000</v>
+        <v>16190000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6970 за поставленный товар</t>
+          <t>Tova uchun to'lov, hisob-faktura №7402 14.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -3738,31 +3738,31 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>15930000</v>
+        <v>43892000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Urganch Avto Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>326351890</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000431509989001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №8745 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3777,33 +3777,33 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>18227000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>32423000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Non XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305567444</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000363109450001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Предоплата за товар по договору №262/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
@@ -3818,33 +3818,33 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>18227000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>27692000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Оплата по с/ф №4447 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3859,40 +3859,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>60502000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>22069000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Gulshan Non XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>305567444</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000363109450001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №286/26</t>
+          <t>Предоплата за товар по договору №128/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3902,38 +3902,38 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>180930000</v>
+        <v>19284000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4402</t>
+          <t>Оплата за продукцию по дог. №91/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3943,38 +3943,38 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>78677000</v>
+        <v>15837000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №262/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №166/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3984,38 +3984,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>17840000</v>
+        <v>10681000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7933 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4024,39 +4024,39 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>74024000</v>
+        <v>18227000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №95/26</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮЛЬ 2026 Г.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>29857000</v>
+        <v>18227000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
@@ -4090,14 +4090,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4105,40 +4105,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>57811000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>194521000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2498 24.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №8614</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4146,40 +4146,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>15464000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>209781000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Navoiy Dori-Darmon AJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>224739659</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000764387001001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8903 за поставленный товар</t>
+          <t>Оплата за сырье по договору №208/26 от 18.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4189,31 +4189,31 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>13629000</v>
+        <v>54613000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №106/26, НДС 12%</t>
+          <t>Shartnoma №206/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -4230,31 +4230,31 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>12045000</v>
+        <v>28934000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5378 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2532 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4269,33 +4269,33 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>11111000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>23736000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Andijon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>292567706</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000683921538001</t>
+          <t>20208000923047387001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по дог. №195/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4310,40 +4310,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>28481000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>13524000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2117</t>
+          <t>Оплата за товар по счет-фактуре №1333 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4351,35 +4351,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>230500000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>12203000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
+          <t>Bahor Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>16307000256038610417</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по с/ф №9554 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4394,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>1652689000</v>
+        <v>12094000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6266 27.08.2026, QQS BILAN</t>
+          <t>Оплата по с/ф №6494 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4433,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>23433000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>10785000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Andijon Meva-Sabzavot AJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>323554683</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000641184978001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №157/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №1220 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4470,39 +4475,39 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>187180000</v>
+        <v>29978000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №82/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4515,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>21325000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>197005000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7014 28.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №282/26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4556,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>24442000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>50379000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3413</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №292/26 ОТ 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4593,17 +4598,17 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>300000</v>
+        <v>230500000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>16307000256038610417</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4613,14 +4618,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4629,39 +4634,39 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>32514000</v>
+        <v>430171000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №208/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №121/26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4669,23 +4674,23 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>56265000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>104965000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4695,14 +4700,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6041</t>
+          <t>Оплата за товар по с/ф №285 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4712,38 +4717,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>180172000</v>
+        <v>9600000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2825 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4751,40 +4756,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>29327000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>11111000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000627281556001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №201/26, НДС 12%</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4794,38 +4799,38 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>35251000</v>
+        <v>21461000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №17/26 от 03.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №8565 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,23 +4838,23 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>467758000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>19898000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4859,14 +4864,14 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №299/26 от 03.09.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3039 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4874,23 +4879,23 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>394188000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>50430000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4900,14 +4905,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3821 от 04.09.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №263/26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>23955000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>120306000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №176/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №31/26 от 27.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4956,23 +4961,23 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>25452000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>59734000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4982,14 +4987,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №67/26 ОТ 04.09.2026, НДС 12%</t>
+          <t>Оплата по с/ф №8562 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4999,38 +5004,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>199209000</v>
+        <v>11543000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №171/26 от 07.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №3375 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5040,38 +5045,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>80675000</v>
+        <v>62946000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Navro'z Polimer XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>297333616</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000293550767001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Shartnoma №210/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №88/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5081,38 +5086,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>34520000</v>
+        <v>25355000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №273/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №369 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5122,38 +5127,38 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>21469000</v>
+        <v>13736000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2971 за поставленный товар</t>
+          <t>Оплата по с/ф №7755 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5161,23 +5166,23 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>26434000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>12242000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Shahrisabz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>273965937</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>20208000438700110001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5187,14 +5192,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №821</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5167</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5203,39 +5208,34 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>26724000</v>
+        <v>300000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>292452726</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №158/26</t>
+          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5244,22 +5244,22 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>139083000</v>
+        <v>40096000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5269,14 +5269,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №200/26 от 07.09.2026, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №292/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5284,35 +5284,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>153838000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>103275000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Bahor Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по с/ф №4192 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,23 +5325,23 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>355317000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>120574000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5346,14 +5351,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7983</t>
+          <t>Предоплата за товар по договору №57/26 от 03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5361,40 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>20460000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>49072000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>395726929</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000499848805001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №31/24</t>
+          <t>Оплата за продукцию по договору №190/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,40 +5407,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>295802000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>44775000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Ip-Kalava MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>211415609</t>
+          <t>271295783</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000851284901001</t>
+          <t>20208000847836346001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №100/26, НДС 12%</t>
+          <t>Оплата за сырье по дог. №132/26 от 04.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5448,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>136347000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>964644000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Xiva Metall MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>326929049</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000848805968001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №84/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8910</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5484,40 +5489,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>46741000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>55944000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №130/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №234/26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5525,40 +5530,35 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>35665000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>153838000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bekobod Meva-Sabzavot AJ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>356979923</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000568584170001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №68/26, НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №7949</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5568,38 +5568,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>205583000</v>
+        <v>61642000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №111/26 от 14.09.2026</t>
+          <t>Shartnoma №225/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5609,38 +5609,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>28618000</v>
+        <v>54381000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №187/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №2/26 от 09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>21832000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>339870886</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000153283399001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6126 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №65/23</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5690,39 +5690,39 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>20978000</v>
+        <v>61479000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Metall MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326929049</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000848805968001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата за транспортные услуги по дог. №223/26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5731,39 +5731,39 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>20978000</v>
+        <v>274712000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Оплата за товары согласно с/ф №5421</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5772,39 +5772,39 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>105246000</v>
+        <v>376785000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №164/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №6605</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5812,40 +5812,40 @@
           <t>229</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>58408000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>79966000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Andijon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>292567706</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000923047387001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4295</t>
+          <t>Предоплата за товар по договору №5/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,21 +5855,21 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>50389000</v>
+        <v>76484000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Andijon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>292567706</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000923047387001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7129 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №277/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5896,38 +5896,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>41728000</v>
+        <v>44108000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Navro'z Non MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>267055674</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000453631094001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №299/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №9164 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>21122000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>93648000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №219/26 ОТ 21.09.2026</t>
+          <t>Оплата за сырье по договору №153/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5977,39 +5977,39 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>32941000</v>
+        <v>20978000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №62/26</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6018,39 +6018,39 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>33749000</v>
+        <v>20978000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9791</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6059,39 +6059,39 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>101527000</v>
+        <v>58111000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo XK</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>278269547</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000297753212001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6406</t>
+          <t>Оплата за сырье по договору №166/26 от 15.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6099,40 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>686092000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>32421000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>270122157</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000360181091001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №234/26</t>
+          <t>Оплата за продукцию по дог. №114/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6141,39 +6141,39 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>33100000</v>
+        <v>44301000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата за упаковочные материалы, с/ф №3821</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6183,21 +6183,21 @@
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>423547000</v>
+        <v>1626176000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Omad Polimer MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>222454209</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000594566369001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3440 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2843 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6224,38 +6224,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>26507000</v>
+        <v>44184000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Yangi Hayot Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>338105674</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000894710105001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №121/26 от 23.09.2026</t>
+          <t>Предоплата за товар по договору №233/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6265,38 +6265,38 @@
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>19681000</v>
+        <v>28250000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mehnat Plastik MChJ</t>
+          <t>Mehnat Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>333224542</t>
+          <t>241560978</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000905945663001</t>
+          <t>20208000128490187001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8864 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №117/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6305,34 +6305,39 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>230500000</v>
+        <v>32455000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>16307000256038610417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6342,38 +6347,38 @@
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>82513000</v>
+        <v>25369000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1345 28.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4932 22.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6383,38 +6388,38 @@
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>29226000</v>
+        <v>185406000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №219/26, НДС 12%</t>
+          <t>Оплата по с/ф №4337 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6423,39 +6428,39 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>12787000</v>
+        <v>86767000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farovon Metall Servis AJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>245272692</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000683921538001</t>
+          <t>20208000225692430001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №149/26 ОТ 25.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6463,40 +6468,35 @@
           <t>245</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>124935000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>230500000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>244420232</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-3304)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>16307000256038610417</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4676 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-3304 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6504,23 +6504,23 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>275965000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>49044000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>292452726</t>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000262256924001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6530,14 +6530,14 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №9625</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9108 28.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6545,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>87864000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>12787000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>244420232</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000488753917001</t>
+          <t>20208000627281556001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №153/26, НДС 12%</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6586,23 +6586,23 @@
           <t>248</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>81473000</v>
-      </c>
+      <c r="C158" s="2" t="n">
+        <v>46005000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shahrisabz Ip-Kalava MChJ</t>
+          <t>Samarqand Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>205381056</t>
+          <t>240244318</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000468947101001</t>
+          <t>20208000695834047001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4427</t>
+          <t>Оплата за сырье по договору №163/26 от 28.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -6627,54 +6627,218 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>66307000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Bahor Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>242023214</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000875391708001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за товар по счет-фактуре №6946 от 30.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="n">
-        <v>7804986000</v>
-      </c>
-      <c r="D160" s="4" t="n">
-        <v>7685486000</v>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>57895000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Angren Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>397992335</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000858417012001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №44/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Oqsaroy Bank ATB</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>45958000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Farg'ona Non XK</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>212215773</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000018109166001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №223/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>107771000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Shahrisabz Non MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>271295783</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000847836346001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по дог. №196/26 от 30.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>7711600000</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>7592100000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C165" s="4" t="n">
         <v>983500000</v>
       </c>
-      <c r="D161" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
